--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t xml:space="preserve">Materials Budget:</t>
   </si>
@@ -62,6 +62,45 @@
   </si>
   <si>
     <t xml:space="preserve">Project Phase: Prototype Build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Stencil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottom Stencil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB Shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB Duty Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB Taxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouser Components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouser Shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouser Duty Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouser Taxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigiKey Components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigiKey Shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigiKey Taxes</t>
   </si>
 </sst>
 </file>
@@ -144,7 +183,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -157,11 +196,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -179,10 +214,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -235,7 +266,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -250,7 +280,6 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -427,7 +456,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -438,12 +467,12 @@
       <c r="C1" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4" t="n">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -453,16 +482,16 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="n">
-        <f aca="false">SUM(E10,E500)</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
+        <f aca="false">SUM(E10:E53)</f>
+        <v>661.26</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4" t="n">
-        <f aca="false">SUM(F10:F56)</f>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="3" t="n">
+        <f aca="false">SUM(F10:F58)</f>
         <v>0</v>
       </c>
     </row>
@@ -473,634 +502,746 @@
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="n">
         <f aca="false">C1-C2</f>
-        <v>2000</v>
-      </c>
-      <c r="E3" s="3" t="s">
+        <v>1338.74</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4" t="n">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="3" t="n">
         <f aca="false">H1-H2</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="n">
         <f aca="false">C10*D10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="n">
         <f aca="false">C11*D11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="n">
         <f aca="false">C12*D12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="n">
         <f aca="false">C13*D13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="n">
         <f aca="false">C14*D14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="n">
         <f aca="false">C15*D15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="n">
         <f aca="false">C17*D17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="n">
         <f aca="false">C18*D18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="n">
         <f aca="false">C19*D19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="n">
         <f aca="false">C20*D20</f>
         <v>0</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="n">
         <f aca="false">C21*D21</f>
         <v>0</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="n">
         <f aca="false">C22*D22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="7" t="s">
+      <c r="B29" s="5"/>
+      <c r="C29" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="2"/>
+      <c r="A30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>8.11</v>
+      </c>
       <c r="E30" s="2" t="n">
         <f aca="false">C30*D30</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
+        <v>81.1</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="2"/>
+      <c r="A31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>15.43</v>
+      </c>
       <c r="E31" s="2" t="n">
         <f aca="false">C31*D31</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
+        <v>15.43</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="2"/>
+      <c r="A32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>15.43</v>
+      </c>
       <c r="E32" s="2" t="n">
         <f aca="false">C32*D32</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
+        <v>15.43</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="2"/>
+      <c r="A33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>83.57</v>
+      </c>
       <c r="E33" s="2" t="n">
         <f aca="false">C33*D33</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
+        <v>83.57</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="2"/>
+      <c r="A34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>67.36</v>
+      </c>
       <c r="E34" s="2" t="n">
         <f aca="false">C34*D34</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
+        <v>67.36</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="2"/>
+      <c r="A35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="E35" s="2" t="n">
         <f aca="false">C35*D35</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
+        <v>13.2</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="2"/>
+      <c r="A36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>308.53</v>
+      </c>
       <c r="E36" s="2" t="n">
         <f aca="false">C36*D36</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
+        <v>308.53</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="2"/>
+      <c r="A37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>10.99</v>
+      </c>
       <c r="E37" s="2" t="n">
         <f aca="false">C37*D37</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+        <v>10.99</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="2"/>
+      <c r="A38" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>49.52</v>
+      </c>
       <c r="E38" s="2" t="n">
         <f aca="false">C38*D38</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
+        <v>49.52</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="7"/>
+      <c r="A39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2" t="n">
         <f aca="false">C39*D39</f>
         <v>0</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="2"/>
+      <c r="A40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>8.12</v>
+      </c>
       <c r="E40" s="2" t="n">
         <f aca="false">C40*D40</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
+        <v>8.12</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="2"/>
+      <c r="A41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>6.99</v>
+      </c>
       <c r="E41" s="2" t="n">
         <f aca="false">C41*D41</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
+        <v>6.99</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="2"/>
+      <c r="A42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1.02</v>
+      </c>
       <c r="E42" s="2" t="n">
         <f aca="false">C42*D42</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
+        <v>1.02</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2" t="n">
+        <f aca="false">C43*D43</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2" t="n">
+        <f aca="false">C44*D44</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="79">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A2:B2"/>
@@ -1176,6 +1317,10 @@
     <mergeCell ref="G41:M41"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="G42:M42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="G43:M43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="G44:M44"/>
   </mergeCells>
   <conditionalFormatting sqref="C3">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t xml:space="preserve">Materials Budget:</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t xml:space="preserve">DigiKey Taxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heatsinks and adhesive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digikey Taxes</t>
   </si>
 </sst>
 </file>
@@ -456,7 +462,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -483,7 +489,7 @@
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="n">
         <f aca="false">SUM(E10:E53)</f>
-        <v>661.26</v>
+        <v>684.95</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -502,7 +508,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="n">
         <f aca="false">C1-C2</f>
-        <v>1338.74</v>
+        <v>1315.05</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1205,13 +1211,19 @@
       <c r="M42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
+      <c r="A43" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="2"/>
+      <c r="C43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>15.64</v>
+      </c>
       <c r="E43" s="2" t="n">
         <f aca="false">C43*D43</f>
-        <v>0</v>
+        <v>15.64</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="8"/>
@@ -1223,13 +1235,19 @@
       <c r="M43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
+      <c r="A44" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="2"/>
+      <c r="C44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1.06</v>
+      </c>
       <c r="E44" s="2" t="n">
         <f aca="false">C44*D44</f>
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="8"/>
@@ -1240,8 +1258,86 @@
       <c r="L44" s="8"/>
       <c r="M44" s="8"/>
     </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <f aca="false">C45*D45</f>
+        <v>6.99</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2" t="n">
+        <f aca="false">C46*D46</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="n">
+        <f aca="false">C47*D47</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2" t="n">
+        <f aca="false">C48*D48</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="79">
+  <mergeCells count="87">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A2:B2"/>
@@ -1321,6 +1417,14 @@
     <mergeCell ref="G43:M43"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="G44:M44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="G45:M45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="G46:M46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="G47:M47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="G48:M48"/>
   </mergeCells>
   <conditionalFormatting sqref="C3">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t xml:space="preserve">Materials Budget:</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t xml:space="preserve">Digikey Taxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable Power Resistor</t>
   </si>
 </sst>
 </file>
@@ -489,7 +492,7 @@
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="n">
         <f aca="false">SUM(E10:E53)</f>
-        <v>684.95</v>
+        <v>719.95</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -508,7 +511,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="n">
         <f aca="false">C1-C2</f>
-        <v>1315.05</v>
+        <v>1280.05</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1283,13 +1286,19 @@
       <c r="M45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5"/>
+      <c r="A46" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="2"/>
+      <c r="C46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>35</v>
+      </c>
       <c r="E46" s="2" t="n">
         <f aca="false">C46*D46</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="8"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t xml:space="preserve">Materials Budget:</t>
   </si>
@@ -91,9 +91,6 @@
     <t xml:space="preserve">Mouser Duty Fee</t>
   </si>
   <si>
-    <t xml:space="preserve">Mouser Taxes</t>
-  </si>
-  <si>
     <t xml:space="preserve">DigiKey Components</t>
   </si>
   <si>
@@ -110,6 +107,36 @@
   </si>
   <si>
     <t xml:space="preserve">Variable Power Resistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel Ammeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Adapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Connector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banana Plugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nylon Standoffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouser – Light Pipes</t>
   </si>
 </sst>
 </file>
@@ -465,7 +492,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -491,8 +518,8 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="n">
-        <f aca="false">SUM(E10:E53)</f>
-        <v>719.95</v>
+        <f aca="false">SUM(E10:E89)</f>
+        <v>906.14</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -500,7 +527,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="3" t="n">
-        <f aca="false">SUM(F10:F58)</f>
+        <f aca="false">SUM(F10:F57)</f>
         <v>0</v>
       </c>
     </row>
@@ -511,7 +538,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="n">
         <f aca="false">C1-C2</f>
-        <v>1280.05</v>
+        <v>1093.86</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -1127,10 +1154,12 @@
       <c r="C39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" s="2" t="n">
+        <v>8.12</v>
+      </c>
       <c r="E39" s="2" t="n">
         <f aca="false">C39*D39</f>
-        <v>0</v>
+        <v>8.12</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="8"/>
@@ -1150,11 +1179,11 @@
         <v>1</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8.12</v>
+        <v>6.99</v>
       </c>
       <c r="E40" s="2" t="n">
         <f aca="false">C40*D40</f>
-        <v>8.12</v>
+        <v>6.99</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="8"/>
@@ -1174,11 +1203,11 @@
         <v>1</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>6.99</v>
+        <v>1.02</v>
       </c>
       <c r="E41" s="2" t="n">
         <f aca="false">C41*D41</f>
-        <v>6.99</v>
+        <v>1.02</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="8"/>
@@ -1198,11 +1227,11 @@
         <v>1</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.02</v>
+        <v>15.64</v>
       </c>
       <c r="E42" s="2" t="n">
         <f aca="false">C42*D42</f>
-        <v>1.02</v>
+        <v>15.64</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="8"/>
@@ -1222,11 +1251,11 @@
         <v>1</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>15.64</v>
+        <v>1.06</v>
       </c>
       <c r="E43" s="2" t="n">
         <f aca="false">C43*D43</f>
-        <v>15.64</v>
+        <v>1.06</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="8"/>
@@ -1237,20 +1266,20 @@
       <c r="L43" s="8"/>
       <c r="M43" s="8"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1.06</v>
+        <v>6.99</v>
       </c>
       <c r="E44" s="2" t="n">
         <f aca="false">C44*D44</f>
-        <v>1.06</v>
+        <v>6.99</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="8"/>
@@ -1263,18 +1292,18 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>6.99</v>
+        <v>35</v>
       </c>
       <c r="E45" s="2" t="n">
         <f aca="false">C45*D45</f>
-        <v>6.99</v>
+        <v>35</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="8"/>
@@ -1294,11 +1323,11 @@
         <v>1</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E46" s="2" t="n">
         <f aca="false">C46*D46</f>
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="8"/>
@@ -1310,13 +1339,19 @@
       <c r="M46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5"/>
+      <c r="A47" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="2"/>
+      <c r="C47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>23.99</v>
+      </c>
       <c r="E47" s="2" t="n">
         <f aca="false">C47*D47</f>
-        <v>0</v>
+        <v>23.99</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="8"/>
@@ -1328,13 +1363,19 @@
       <c r="M47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
+      <c r="A48" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="B48" s="5"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="2"/>
+      <c r="C48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>17.95</v>
+      </c>
       <c r="E48" s="2" t="n">
         <f aca="false">C48*D48</f>
-        <v>0</v>
+        <v>17.95</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="8"/>
@@ -1345,8 +1386,290 @@
       <c r="L48" s="8"/>
       <c r="M48" s="8"/>
     </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <f aca="false">C49*D49</f>
+        <v>6.39</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <f aca="false">C50*D50</f>
+        <v>7.97</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <f aca="false">C51*D51</f>
+        <v>5.99</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <f aca="false">C52*D52</f>
+        <v>20.98</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <f aca="false">C53*D53</f>
+        <v>50.97</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <f aca="false">C54*D54</f>
+        <v>20</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <f aca="false">C55*D55</f>
+        <v>6.99</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <f aca="false">C56*D56</f>
+        <v>15.96</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2" t="n">
+        <f aca="false">C57*D57</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2" t="n">
+        <f aca="false">C58*D58</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2" t="n">
+        <f aca="false">C59*D59</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2" t="n">
+        <f aca="false">C60*D60</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2" t="n">
+        <f aca="false">C61*D61</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="113">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A2:B2"/>
@@ -1434,6 +1757,32 @@
     <mergeCell ref="G47:M47"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="G48:M48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="G49:M49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="G50:M50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="G52:M52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="G53:M53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="G54:M54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="G55:M55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="G56:M56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="G57:M57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="G58:M58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="G59:M59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="G60:M60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="G61:M61"/>
   </mergeCells>
   <conditionalFormatting sqref="C3">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/P1012202501-Project_Budget.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t xml:space="preserve">Materials Budget:</t>
   </si>
@@ -137,6 +137,15 @@
   </si>
   <si>
     <t xml:space="preserve">Mouser – Light Pipes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Phase: First Revision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rev 2 PCBs and Stencils</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 US to UART ICs</t>
   </si>
 </sst>
 </file>
@@ -492,7 +501,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -518,8 +527,8 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="n">
-        <f aca="false">SUM(E10:E89)</f>
-        <v>906.14</v>
+        <f aca="false">SUM(E10:E200)</f>
+        <v>1185.99</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -527,7 +536,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="3" t="n">
-        <f aca="false">SUM(F10:F57)</f>
+        <f aca="false">SUM(F10:F55)</f>
         <v>0</v>
       </c>
     </row>
@@ -538,7 +547,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="n">
         <f aca="false">C1-C2</f>
-        <v>1093.86</v>
+        <v>814.01</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -878,72 +887,111 @@
       <c r="M25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
+      <c r="A26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
+      <c r="C28" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>8.11</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <f aca="false">C28*D28</f>
+        <v>81.1</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
+      <c r="C29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <f aca="false">C29*D29</f>
+        <v>15.43</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8.11</v>
+        <v>15.43</v>
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">C30*D30</f>
-        <v>81.1</v>
+        <v>15.43</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="8"/>
@@ -956,18 +1004,18 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>15.43</v>
+        <v>83.57</v>
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">C31*D31</f>
-        <v>15.43</v>
+        <v>83.57</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="8"/>
@@ -980,18 +1028,18 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15.43</v>
+        <v>67.36</v>
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">C32*D32</f>
-        <v>15.43</v>
+        <v>67.36</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="8"/>
@@ -1004,18 +1052,18 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>83.57</v>
+        <v>13.2</v>
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">C33*D33</f>
-        <v>83.57</v>
+        <v>13.2</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="8"/>
@@ -1028,18 +1076,18 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>67.36</v>
+        <v>308.53</v>
       </c>
       <c r="E34" s="2" t="n">
         <f aca="false">C34*D34</f>
-        <v>67.36</v>
+        <v>308.53</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="8"/>
@@ -1052,18 +1100,18 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>13.2</v>
+        <v>10.99</v>
       </c>
       <c r="E35" s="2" t="n">
         <f aca="false">C35*D35</f>
-        <v>13.2</v>
+        <v>10.99</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="8"/>
@@ -1076,18 +1124,18 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>308.53</v>
+        <v>49.52</v>
       </c>
       <c r="E36" s="2" t="n">
         <f aca="false">C36*D36</f>
-        <v>308.53</v>
+        <v>49.52</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="8"/>
@@ -1100,18 +1148,18 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10.99</v>
+        <v>8.12</v>
       </c>
       <c r="E37" s="2" t="n">
         <f aca="false">C37*D37</f>
-        <v>10.99</v>
+        <v>8.12</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="8"/>
@@ -1124,18 +1172,18 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>49.52</v>
+        <v>6.99</v>
       </c>
       <c r="E38" s="2" t="n">
         <f aca="false">C38*D38</f>
-        <v>49.52</v>
+        <v>6.99</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="8"/>
@@ -1148,18 +1196,18 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8.12</v>
+        <v>1.02</v>
       </c>
       <c r="E39" s="2" t="n">
         <f aca="false">C39*D39</f>
-        <v>8.12</v>
+        <v>1.02</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="8"/>
@@ -1172,18 +1220,18 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>6.99</v>
+        <v>15.64</v>
       </c>
       <c r="E40" s="2" t="n">
         <f aca="false">C40*D40</f>
-        <v>6.99</v>
+        <v>15.64</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="8"/>
@@ -1196,18 +1244,18 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="E41" s="2" t="n">
         <f aca="false">C41*D41</f>
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="8"/>
@@ -1218,20 +1266,20 @@
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>15.64</v>
+        <v>6.99</v>
       </c>
       <c r="E42" s="2" t="n">
         <f aca="false">C42*D42</f>
-        <v>15.64</v>
+        <v>6.99</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="8"/>
@@ -1242,20 +1290,20 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.06</v>
+        <v>35</v>
       </c>
       <c r="E43" s="2" t="n">
         <f aca="false">C43*D43</f>
-        <v>1.06</v>
+        <v>35</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="8"/>
@@ -1268,18 +1316,18 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>6.99</v>
+        <v>9</v>
       </c>
       <c r="E44" s="2" t="n">
         <f aca="false">C44*D44</f>
-        <v>6.99</v>
+        <v>9</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="8"/>
@@ -1292,18 +1340,18 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>35</v>
+        <v>23.99</v>
       </c>
       <c r="E45" s="2" t="n">
         <f aca="false">C45*D45</f>
-        <v>35</v>
+        <v>23.99</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="8"/>
@@ -1316,18 +1364,18 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>9</v>
+        <v>17.95</v>
       </c>
       <c r="E46" s="2" t="n">
         <f aca="false">C46*D46</f>
-        <v>9</v>
+        <v>17.95</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="8"/>
@@ -1340,18 +1388,18 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>23.99</v>
+        <v>6.39</v>
       </c>
       <c r="E47" s="2" t="n">
         <f aca="false">C47*D47</f>
-        <v>23.99</v>
+        <v>6.39</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="8"/>
@@ -1364,18 +1412,18 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>17.95</v>
+        <v>7.97</v>
       </c>
       <c r="E48" s="2" t="n">
         <f aca="false">C48*D48</f>
-        <v>17.95</v>
+        <v>7.97</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="8"/>
@@ -1388,18 +1436,18 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>6.39</v>
+        <v>5.99</v>
       </c>
       <c r="E49" s="2" t="n">
         <f aca="false">C49*D49</f>
-        <v>6.39</v>
+        <v>5.99</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="8"/>
@@ -1412,18 +1460,18 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>7.97</v>
+        <v>10.49</v>
       </c>
       <c r="E50" s="2" t="n">
         <f aca="false">C50*D50</f>
-        <v>7.97</v>
+        <v>20.98</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="8"/>
@@ -1436,18 +1484,18 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5.99</v>
+        <v>16.99</v>
       </c>
       <c r="E51" s="2" t="n">
         <f aca="false">C51*D51</f>
-        <v>5.99</v>
+        <v>50.97</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="8"/>
@@ -1460,18 +1508,18 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10.49</v>
+        <v>20</v>
       </c>
       <c r="E52" s="2" t="n">
         <f aca="false">C52*D52</f>
-        <v>20.98</v>
+        <v>20</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="8"/>
@@ -1484,18 +1532,18 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>16.99</v>
+        <v>6.99</v>
       </c>
       <c r="E53" s="2" t="n">
         <f aca="false">C53*D53</f>
-        <v>50.97</v>
+        <v>6.99</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="8"/>
@@ -1508,18 +1556,18 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>20</v>
+        <v>15.96</v>
       </c>
       <c r="E54" s="2" t="n">
         <f aca="false">C54*D54</f>
-        <v>20</v>
+        <v>15.96</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="8"/>
@@ -1531,19 +1579,13 @@
       <c r="M54" s="8"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="A55" s="5"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>6.99</v>
-      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="2"/>
       <c r="E55" s="2" t="n">
         <f aca="false">C55*D55</f>
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="8"/>
@@ -1555,19 +1597,13 @@
       <c r="M55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="A56" s="5"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>15.96</v>
-      </c>
+      <c r="C56" s="6"/>
+      <c r="D56" s="2"/>
       <c r="E56" s="2" t="n">
         <f aca="false">C56*D56</f>
-        <v>15.96</v>
+        <v>0</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="8"/>
@@ -1632,44 +1668,496 @@
       <c r="L59" s="8"/>
       <c r="M59" s="8"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2" t="n">
-        <f aca="false">C60*D60</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
-      <c r="M60" s="8"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2" t="n">
-        <f aca="false">C61*D61</f>
-        <v>0</v>
-      </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>235.56</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <f aca="false">C65*D65</f>
+        <v>235.56</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="5"/>
+      <c r="C66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <f aca="false">C66*D66</f>
+        <v>44.29</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="8"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2" t="n">
+        <f aca="false">C67*D67</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2" t="n">
+        <f aca="false">C68*D68</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2" t="n">
+        <f aca="false">C69*D69</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="3"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2" t="n">
+        <f aca="false">C70*D70</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="3"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2" t="n">
+        <f aca="false">C71*D71</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="3"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2" t="n">
+        <f aca="false">C72*D72</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2" t="n">
+        <f aca="false">C73*D73</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="3"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2" t="n">
+        <f aca="false">C74*D74</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2" t="n">
+        <f aca="false">C75*D75</f>
+        <v>0</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2" t="n">
+        <f aca="false">C76*D76</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2" t="n">
+        <f aca="false">C77*D77</f>
+        <v>0</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2" t="n">
+        <f aca="false">C78*D78</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2" t="n">
+        <f aca="false">C79*D79</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2" t="n">
+        <f aca="false">C80*D80</f>
+        <v>0</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2" t="n">
+        <f aca="false">C81*D81</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2" t="n">
+        <f aca="false">C82*D82</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="M82" s="8"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2" t="n">
+        <f aca="false">C83*D83</f>
+        <v>0</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2" t="n">
+        <f aca="false">C84*D84</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2" t="n">
+        <f aca="false">C85*D85</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2" t="n">
+        <f aca="false">C86*D86</f>
+        <v>0</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2" t="n">
+        <f aca="false">C87*D87</f>
+        <v>0</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2" t="n">
+        <f aca="false">C88*D88</f>
+        <v>0</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="113">
+  <mergeCells count="163">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A2:B2"/>
@@ -1715,8 +2203,11 @@
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="G25:M25"/>
-    <mergeCell ref="G26:M26"/>
-    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="G27:M27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="G28:M28"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="G29:M29"/>
     <mergeCell ref="A30:B30"/>
@@ -1779,10 +2270,57 @@
     <mergeCell ref="G58:M58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="G59:M59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="G60:M60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="G61:M61"/>
+    <mergeCell ref="A63:M63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="G64:M64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="G65:M65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="G66:M66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="G67:M67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="G68:M68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="G69:M69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="G70:M70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="G71:M71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="G72:M72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="G73:M73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="G74:M74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="G75:M75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="G76:M76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="G77:M77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="G78:M78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="G79:M79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="G80:M80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="G81:M81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="G82:M82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="G83:M83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="G84:M84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="G85:M85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="G86:M86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="G87:M87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="G88:M88"/>
   </mergeCells>
   <conditionalFormatting sqref="C3">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
